--- a/Assignment/testdata/bookingData.xlsx
+++ b/Assignment/testdata/bookingData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SAMEER-PC\eclipse-workspace\Assignment\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2A31AAE-822F-4B2C-A397-93DD916C2B9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{498ECC6D-1492-41F2-87C8-A5E3699DF41A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2843" yWindow="2160" windowWidth="16117" windowHeight="9293" xr2:uid="{5437E27C-3892-452C-A3C5-7537AD17C495}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{5437E27C-3892-452C-A3C5-7537AD17C495}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="10">
   <si>
     <t>John</t>
   </si>
@@ -63,6 +63,9 @@
   </si>
   <si>
     <t>CheckOutDt</t>
+  </si>
+  <si>
+    <t>+919090909090</t>
   </si>
 </sst>
 </file>
@@ -462,8 +465,7 @@
   <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="4" max="4" width="9.06640625" style="2"/>
-    <col min="5" max="5" width="10.73046875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="10.73046875" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.796875" style="2" customWidth="1"/>
   </cols>
   <sheetData>
@@ -497,8 +499,8 @@
       <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="2">
-        <v>2</v>
+      <c r="D2" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="E2" s="3">
         <v>46143</v>
@@ -517,8 +519,8 @@
       <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="2">
-        <v>2</v>
+      <c r="D3" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="E3" s="3">
         <v>46143</v>
@@ -537,8 +539,8 @@
       <c r="C4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="2">
-        <v>2</v>
+      <c r="D4" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="E4" s="3">
         <v>46143</v>
